--- a/DASHBOARDS/HR ANALYSIS/hr data_analysis_dashbaord.xlsx
+++ b/DASHBOARDS/HR ANALYSIS/hr data_analysis_dashbaord.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kython.DESKTOP-V776MIM\Downloads\analist\projects\HR ANALYSIS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kython.DESKTOP-V776MIM\Documents\git repos\profile\EXCELL\DASHBOARDS\HR ANALYSIS\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -22,7 +22,7 @@
   </definedNames>
   <calcPr calcId="152511"/>
   <pivotCaches>
-    <pivotCache cacheId="1" r:id="rId4"/>
+    <pivotCache cacheId="0" r:id="rId4"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
@@ -964,85 +964,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="42">
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFFFD757"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="1" tint="0.499984740745262"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <fgColor theme="1" tint="0.14996795556505021"/>
-          <bgColor theme="1" tint="0.14996795556505021"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.0"/>
-    </dxf>
+  <dxfs count="28">
     <dxf>
       <numFmt numFmtId="164" formatCode="0.0"/>
     </dxf>
@@ -1800,11 +1722,47 @@
     <dxf>
       <numFmt numFmtId="164" formatCode="0.0"/>
     </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFFD757"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="1" tint="0.499984740745262"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <fgColor theme="1" tint="0.14996795556505021"/>
+          <bgColor theme="1" tint="0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
   </dxfs>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
     <tableStyle name="MINE" pivot="0" table="0" count="3">
-      <tableStyleElement type="wholeTable" dxfId="1"/>
-      <tableStyleElement type="headerRow" dxfId="0"/>
+      <tableStyleElement type="wholeTable" dxfId="27"/>
+      <tableStyleElement type="headerRow" dxfId="26"/>
     </tableStyle>
   </tableStyles>
   <colors>
@@ -1818,31 +1776,7 @@
   </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{46F421CA-312F-682f-3DD2-61675219B42D}">
-      <x14:dxfs count="4">
-        <dxf>
-          <fill>
-            <patternFill>
-              <fgColor rgb="FFFFFF00"/>
-              <bgColor rgb="FFFFD757"/>
-            </patternFill>
-          </fill>
-        </dxf>
-        <dxf>
-          <fill>
-            <patternFill>
-              <fgColor rgb="FFFFFF00"/>
-              <bgColor rgb="FFFFD757"/>
-            </patternFill>
-          </fill>
-        </dxf>
-        <dxf>
-          <fill>
-            <patternFill>
-              <fgColor rgb="FFFFFF00"/>
-              <bgColor rgb="FFFFD757"/>
-            </patternFill>
-          </fill>
-        </dxf>
+      <x14:dxfs count="1">
         <dxf>
           <fill>
             <patternFill>
@@ -2317,11 +2251,11 @@
         </c:dLbls>
         <c:gapWidth val="150"/>
         <c:overlap val="100"/>
-        <c:axId val="193617104"/>
-        <c:axId val="193617648"/>
+        <c:axId val="1834039056"/>
+        <c:axId val="1834033072"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="193617104"/>
+        <c:axId val="1834039056"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2331,7 +2265,7 @@
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="193617648"/>
+        <c:crossAx val="1834033072"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2339,7 +2273,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="193617648"/>
+        <c:axId val="1834033072"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2349,7 +2283,7 @@
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="193617104"/>
+        <c:crossAx val="1834039056"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2557,11 +2491,11 @@
         </c:dLbls>
         <c:gapWidth val="150"/>
         <c:overlap val="100"/>
-        <c:axId val="193619824"/>
-        <c:axId val="193618736"/>
+        <c:axId val="1834045040"/>
+        <c:axId val="1834039600"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="193619824"/>
+        <c:axId val="1834045040"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2571,7 +2505,7 @@
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="193618736"/>
+        <c:crossAx val="1834039600"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2579,7 +2513,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="193618736"/>
+        <c:axId val="1834039600"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2589,7 +2523,7 @@
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="193619824"/>
+        <c:crossAx val="1834045040"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2807,11 +2741,11 @@
         </c:dLbls>
         <c:gapWidth val="150"/>
         <c:overlap val="100"/>
-        <c:axId val="193621456"/>
-        <c:axId val="193619280"/>
+        <c:axId val="1834026000"/>
+        <c:axId val="1834033616"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="193621456"/>
+        <c:axId val="1834026000"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2821,7 +2755,7 @@
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="193619280"/>
+        <c:crossAx val="1834033616"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2829,7 +2763,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="193619280"/>
+        <c:axId val="1834033616"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2839,7 +2773,7 @@
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="193621456"/>
+        <c:crossAx val="1834026000"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3029,11 +2963,11 @@
         </c:dLbls>
         <c:gapWidth val="100"/>
         <c:overlap val="-24"/>
-        <c:axId val="190496992"/>
-        <c:axId val="190497536"/>
+        <c:axId val="1834027088"/>
+        <c:axId val="1834043408"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="190496992"/>
+        <c:axId val="1834027088"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3075,7 +3009,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="190497536"/>
+        <c:crossAx val="1834043408"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3083,7 +3017,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="190497536"/>
+        <c:axId val="1834043408"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3107,7 +3041,7 @@
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="190496992"/>
+        <c:crossAx val="1834027088"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3952,11 +3886,11 @@
         </c:dLbls>
         <c:gapWidth val="219"/>
         <c:overlap val="-27"/>
-        <c:axId val="190488832"/>
-        <c:axId val="190495360"/>
+        <c:axId val="1834042320"/>
+        <c:axId val="1834043952"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="190488832"/>
+        <c:axId val="1834042320"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4001,7 +3935,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="190495360"/>
+        <c:crossAx val="1834043952"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4009,7 +3943,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="190495360"/>
+        <c:axId val="1834043952"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4019,7 +3953,7 @@
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="190488832"/>
+        <c:crossAx val="1834042320"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4308,11 +4242,11 @@
         </c:dLbls>
         <c:gapWidth val="150"/>
         <c:overlap val="100"/>
-        <c:axId val="190499168"/>
-        <c:axId val="190489376"/>
+        <c:axId val="1834021104"/>
+        <c:axId val="1834031984"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="190499168"/>
+        <c:axId val="1834021104"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4322,7 +4256,7 @@
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="190489376"/>
+        <c:crossAx val="1834031984"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4330,7 +4264,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="190489376"/>
+        <c:axId val="1834031984"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4340,7 +4274,7 @@
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="190499168"/>
+        <c:crossAx val="1834021104"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4480,7 +4414,6 @@
             <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:layout/>
                 <c15:showLeaderLines val="1"/>
                 <c15:leaderLines>
                   <c:spPr>
@@ -4545,11 +4478,11 @@
         </c:dLbls>
         <c:gapWidth val="182"/>
         <c:overlap val="100"/>
-        <c:axId val="190490464"/>
-        <c:axId val="190500800"/>
+        <c:axId val="1834023280"/>
+        <c:axId val="1834034704"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="190490464"/>
+        <c:axId val="1834023280"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4559,7 +4492,7 @@
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="190500800"/>
+        <c:crossAx val="1834034704"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4567,7 +4500,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="190500800"/>
+        <c:axId val="1834034704"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4577,7 +4510,7 @@
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="190490464"/>
+        <c:crossAx val="1834023280"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5065,7 +4998,6 @@
             <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:layout/>
                 <c15:showLeaderLines val="1"/>
                 <c15:leaderLines>
                   <c:spPr>
@@ -5547,11 +5479,11 @@
         </c:dLbls>
         <c:gapWidth val="219"/>
         <c:overlap val="-27"/>
-        <c:axId val="190486656"/>
-        <c:axId val="190492096"/>
+        <c:axId val="1834041776"/>
+        <c:axId val="1834032528"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="190486656"/>
+        <c:axId val="1834041776"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5561,7 +5493,7 @@
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="190492096"/>
+        <c:crossAx val="1834032528"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -5569,7 +5501,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="190492096"/>
+        <c:axId val="1834032528"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5594,7 +5526,7 @@
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="190486656"/>
+        <c:crossAx val="1834041776"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -6188,11 +6120,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="182"/>
-        <c:axId val="190495904"/>
-        <c:axId val="190492640"/>
+        <c:axId val="1834030352"/>
+        <c:axId val="1834022736"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="190495904"/>
+        <c:axId val="1834030352"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6202,7 +6134,7 @@
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="190492640"/>
+        <c:crossAx val="1834022736"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -6210,7 +6142,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="190492640"/>
+        <c:axId val="1834022736"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6230,7 +6162,7 @@
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="190495904"/>
+        <c:crossAx val="1834030352"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -17342,6 +17274,7 @@
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="Calibri"/>
             </a:rPr>
+            <a:pPr marL="0" indent="0" algn="ctr"/>
             <a:t>52%</a:t>
           </a:fld>
           <a:endParaRPr lang="en-US" sz="1800" b="0" i="0" u="none" strike="noStrike" baseline="0">
@@ -18917,8 +18850,8 @@
       <xdr:row>5</xdr:row>
       <xdr:rowOff>23811</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="130" name="Gender"/>
@@ -18935,7 +18868,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -19114,6 +19047,7 @@
               <a:latin typeface="Calibri"/>
               <a:cs typeface="Calibri"/>
             </a:rPr>
+            <a:pPr algn="ctr"/>
             <a:t>50</a:t>
           </a:fld>
           <a:endParaRPr lang="en-US" sz="6600" b="1">
@@ -19781,6 +19715,7 @@
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="Calibri"/>
             </a:rPr>
+            <a:pPr marL="0" indent="0" algn="ctr"/>
             <a:t>20</a:t>
           </a:fld>
           <a:endParaRPr lang="en-US" sz="6000" b="1" i="0" u="none" strike="noStrike">
@@ -21110,7 +21045,668 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable3" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="5" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="5" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="D19:E25" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="21">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="3">
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="6">
+        <item x="4"/>
+        <item x="1"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="6">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="4"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="6"/>
+  </rowFields>
+  <rowItems count="6">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Leave Taken" fld="16" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="employyes skills" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="5" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="L14:M20" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="21">
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0">
+      <items count="3">
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="6">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="4"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="6">
+        <item x="3"/>
+        <item x="0"/>
+        <item x="4"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="19"/>
+  </rowFields>
+  <rowItems count="6">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Count of Full Name" fld="1" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="5" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="L2:O9" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <pivotFields count="21">
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField axis="axisCol" showAll="0">
+      <items count="3">
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="6">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="4"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="6">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="4"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="4">
+        <item x="1"/>
+        <item x="0"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="4"/>
+  </rowFields>
+  <rowItems count="6">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="2"/>
+  </colFields>
+  <colItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Count of Full Name" fld="1" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="3">
+    <chartFormat chart="4" format="6" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="4" format="7" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="4" format="8" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable5" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="5" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="G29:H35" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="21">
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0">
+      <items count="3">
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="6">
+        <item x="1"/>
+        <item x="0"/>
+        <item x="4"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="6">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="4"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="5"/>
+  </rowFields>
+  <rowItems count="6">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Count of Full Name" fld="1" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="salary per department" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="5" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="D2:E8" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="21">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="3">
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="6">
+        <item x="4"/>
+        <item x="1"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="6">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="4"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="6"/>
+  </rowFields>
+  <rowItems count="6">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Salary" fld="12" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="COUNT AS PER STATUS" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="5" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A3:B7" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="21">
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="3">
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="6">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="4"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="4">
+        <item x="1"/>
+        <item x="0"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="10"/>
+  </rowFields>
+  <rowItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Count of Employee ID" fld="0" subtotal="count" baseField="10" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable7" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="5" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="D37:E43" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="21">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="3">
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="6">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="4"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="7"/>
+  </rowFields>
+  <rowItems count="6">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Average of Performance Rating" fld="17" subtotal="average" baseField="7" baseItem="0"/>
+  </dataFields>
+  <formats count="1">
+    <format dxfId="25">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="1">
+          <reference field="7" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable8.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="5" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="L34:M38" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="21">
     <pivotField showAll="0"/>
@@ -21174,8 +21770,8 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="age range to gender" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="5" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5">
+<file path=xl/pivotTables/pivotTable9.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="age range to gender" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="5" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5">
   <location ref="G2:J9" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="21">
     <pivotField showAll="0"/>
@@ -21378,667 +21974,6 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="employyes skills" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="5" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="L14:M20" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="21">
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0">
-      <items count="3">
-        <item x="0"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="6">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="4"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="6">
-        <item x="3"/>
-        <item x="0"/>
-        <item x="4"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="19"/>
-  </rowFields>
-  <rowItems count="6">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Count of Full Name" fld="1" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="salary per department" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="5" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="D2:E8" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="21">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="3">
-        <item x="0"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="6">
-        <item x="4"/>
-        <item x="1"/>
-        <item x="3"/>
-        <item x="2"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="6">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="4"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="6"/>
-  </rowFields>
-  <rowItems count="6">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Sum of Salary" fld="12" baseField="0" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="COUNT AS PER STATUS" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="5" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="A3:B7" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="21">
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="3">
-        <item x="0"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="6">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="4"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="4">
-        <item x="1"/>
-        <item x="0"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="10"/>
-  </rowFields>
-  <rowItems count="4">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Count of Employee ID" fld="0" subtotal="count" baseField="10" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable7" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="5" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="D37:E43" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="21">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="3">
-        <item x="0"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="6">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="4"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="7"/>
-  </rowFields>
-  <rowItems count="6">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Average of Performance Rating" fld="17" subtotal="average" baseField="7" baseItem="0"/>
-  </dataFields>
-  <formats count="1">
-    <format dxfId="41">
-      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
-        <references count="1">
-          <reference field="7" count="0"/>
-        </references>
-      </pivotArea>
-    </format>
-  </formats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable2" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="5" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="D19:E25" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="21">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="3">
-        <item x="0"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="6">
-        <item x="4"/>
-        <item x="1"/>
-        <item x="3"/>
-        <item x="2"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="6">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="4"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="6"/>
-  </rowFields>
-  <rowItems count="6">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Sum of Leave Taken" fld="16" baseField="0" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable8.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable1" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="5" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="L2:O9" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
-  <pivotFields count="21">
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField axis="axisCol" showAll="0">
-      <items count="3">
-        <item x="0"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="6">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="4"/>
-        <item x="3"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="6">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="4"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="4">
-        <item x="1"/>
-        <item x="0"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="4"/>
-  </rowFields>
-  <rowItems count="6">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="2"/>
-  </colFields>
-  <colItems count="3">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Count of Full Name" fld="1" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <chartFormats count="3">
-    <chartFormat chart="4" format="6" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="4" format="7" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="2" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="4" format="8" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="2" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable9.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable5" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="5" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="G29:H35" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="21">
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0">
-      <items count="3">
-        <item x="0"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="6">
-        <item x="1"/>
-        <item x="0"/>
-        <item x="4"/>
-        <item x="3"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="6">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="4"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="5"/>
-  </rowFields>
-  <rowItems count="6">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Count of Full Name" fld="1" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
 <file path=xl/slicerCaches/slicerCache1.xml><?xml version="1.0" encoding="utf-8"?>
 <slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x" name="Slicer_Gender" sourceName="Gender">
   <pivotTables>
@@ -22107,30 +22042,30 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:U51" totalsRowShown="0" headerRowDxfId="40" dataDxfId="39">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:U51" totalsRowShown="0" headerRowDxfId="24" dataDxfId="23">
   <autoFilter ref="A1:U51"/>
   <tableColumns count="21">
-    <tableColumn id="1" name="Employee ID" dataDxfId="38"/>
-    <tableColumn id="2" name="Full Name" dataDxfId="37"/>
-    <tableColumn id="3" name="Gender" dataDxfId="36"/>
-    <tableColumn id="4" name="Age" dataDxfId="35"/>
-    <tableColumn id="5" name="Age range" dataDxfId="34"/>
-    <tableColumn id="6" name="Region" dataDxfId="33"/>
-    <tableColumn id="7" name="Job Title" dataDxfId="32"/>
-    <tableColumn id="8" name="Department" dataDxfId="31"/>
-    <tableColumn id="9" name="Manager/Supervisor" dataDxfId="30"/>
-    <tableColumn id="10" name="Date of Hire" dataDxfId="29"/>
-    <tableColumn id="11" name="Employment Status" dataDxfId="28"/>
-    <tableColumn id="12" name="Work Location" dataDxfId="27"/>
-    <tableColumn id="13" name="Salary" dataDxfId="26"/>
-    <tableColumn id="14" name="Pay Grade" dataDxfId="25"/>
-    <tableColumn id="15" name="Bonus/Allowances" dataDxfId="24"/>
-    <tableColumn id="16" name="Insurance Details" dataDxfId="23"/>
-    <tableColumn id="17" name="Leave Taken" dataDxfId="22"/>
-    <tableColumn id="18" name="Performance Rating" dataDxfId="21"/>
-    <tableColumn id="19" name="Training Programs Attended" dataDxfId="20"/>
-    <tableColumn id="20" name="Skills" dataDxfId="19"/>
-    <tableColumn id="21" name="Certifications" dataDxfId="18"/>
+    <tableColumn id="1" name="Employee ID" dataDxfId="22"/>
+    <tableColumn id="2" name="Full Name" dataDxfId="21"/>
+    <tableColumn id="3" name="Gender" dataDxfId="20"/>
+    <tableColumn id="4" name="Age" dataDxfId="19"/>
+    <tableColumn id="5" name="Age range" dataDxfId="18"/>
+    <tableColumn id="6" name="Region" dataDxfId="17"/>
+    <tableColumn id="7" name="Job Title" dataDxfId="16"/>
+    <tableColumn id="8" name="Department" dataDxfId="15"/>
+    <tableColumn id="9" name="Manager/Supervisor" dataDxfId="14"/>
+    <tableColumn id="10" name="Date of Hire" dataDxfId="13"/>
+    <tableColumn id="11" name="Employment Status" dataDxfId="12"/>
+    <tableColumn id="12" name="Work Location" dataDxfId="11"/>
+    <tableColumn id="13" name="Salary" dataDxfId="10"/>
+    <tableColumn id="14" name="Pay Grade" dataDxfId="9"/>
+    <tableColumn id="15" name="Bonus/Allowances" dataDxfId="8"/>
+    <tableColumn id="16" name="Insurance Details" dataDxfId="7"/>
+    <tableColumn id="17" name="Leave Taken" dataDxfId="6"/>
+    <tableColumn id="18" name="Performance Rating" dataDxfId="5"/>
+    <tableColumn id="19" name="Training Programs Attended" dataDxfId="4"/>
+    <tableColumn id="20" name="Skills" dataDxfId="3"/>
+    <tableColumn id="21" name="Certifications" dataDxfId="2"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -22399,7 +22334,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="R11:U21"/>
+  <dimension ref="T11:U21"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="11" width="9.140625" style="1"/>
